--- a/Result/profitability/2033.xlsx
+++ b/Result/profitability/2033.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.0925</v>
       </c>
       <c r="N2" t="n">
-        <v>13.875</v>
+        <v>14.1625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.91</v>
       </c>
       <c r="M3" t="n">
-        <v>0.19875</v>
+        <v>0.20125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.7675</v>
+        <v>16.0675</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.33</v>
+        <v>0.32375</v>
       </c>
       <c r="N4" t="n">
-        <v>18.29625</v>
+        <v>18.18375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0.23375</v>
+        <v>0.235</v>
       </c>
       <c r="N5" t="n">
-        <v>19.42625</v>
+        <v>19.5775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2125</v>
+        <v>0.20875</v>
       </c>
       <c r="N6" t="n">
-        <v>18.65375</v>
+        <v>18.775</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>0.15375</v>
+        <v>0.15</v>
       </c>
       <c r="N7" t="n">
-        <v>15.735</v>
+        <v>15.79125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.14625</v>
+        <v>0.1425</v>
       </c>
       <c r="N8" t="n">
-        <v>15.80375</v>
+        <v>15.69375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1772,7 +1772,7 @@
         <v>0.47</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0925</v>
+        <v>0.09250000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>15.41375</v>
@@ -1899,7 +1899,7 @@
         <v>0.25</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01250000000000001</v>
+        <v>-0.0125</v>
       </c>
       <c r="N12" t="n">
         <v>13.83125</v>
@@ -2026,7 +2026,7 @@
         <v>0.23</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09874999999999999</v>
+        <v>0.09875</v>
       </c>
       <c r="N13" t="n">
         <v>12.46</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>168</v>
+      </c>
+      <c r="D75" t="n">
+        <v>144</v>
+      </c>
+      <c r="E75" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.96625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.879999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05662805662805659</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.009999999999999995</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.210000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0899628252788105</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
